--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-antofagasta.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4468-104-CM26</t>
+          <t>4291-15-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10503.58</v>
+        <v>52874.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1261592-973-CM26</t>
+          <t>1375735-8-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,6 +630,433 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
+        <v>24653.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1233623-86-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>OFISILLAS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>5890.87</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2385-405-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>78.616.370-6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>8934.530000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2383-4-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.235.755-0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>49989.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2383-5-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>IMPORTADORA PROMSA SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.780.759-7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>11884.32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2429-2700-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>11677.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4468-104-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>10503.58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1261592-973-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>46520.53</v>
       </c>
     </row>
